--- a/Researchland/Base_historica_RL.xlsx
+++ b/Researchland/Base_historica_RL.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\954108\Desktop\codigos_py\Presentaciones\IPN_Colaboradores\Researchland\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC8D959-84F3-4559-8554-D75EC9359186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Periodo</t>
   </si>
@@ -80,16 +86,13 @@
   </si>
   <si>
     <t>1Q´26</t>
-  </si>
-  <si>
-    <t>2Q´26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,13 +129,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -170,7 +181,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -204,6 +215,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -238,9 +250,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -413,11 +426,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,24 +447,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.364</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="C2">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="D2">
-        <v>0.273</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="E2">
         <v>0.182</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -459,16 +472,16 @@
         <v>0.317</v>
       </c>
       <c r="C3">
-        <v>0.512</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="D3">
-        <v>0.293</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="E3">
-        <v>0.195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.19500000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -476,135 +489,135 @@
         <v>0.5</v>
       </c>
       <c r="C4">
-        <v>0.609</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="D4">
-        <v>0.283</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="E4">
         <v>0.109</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.458</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="C5">
-        <v>0.604</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="D5">
         <v>0.25</v>
       </c>
       <c r="E5">
-        <v>0.146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>0.14599999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.652</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="C6">
-        <v>0.674</v>
+        <v>0.67400000000000004</v>
       </c>
       <c r="D6">
-        <v>0.304</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="E6">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.667</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="C7">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="D7">
-        <v>0.286</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="E7">
-        <v>0.024</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.673</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="C8">
-        <v>0.709</v>
+        <v>0.70899999999999996</v>
       </c>
       <c r="D8">
         <v>0.255</v>
       </c>
       <c r="E8">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.587</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="C9">
-        <v>0.667</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="D9">
         <v>0.254</v>
       </c>
       <c r="E9">
-        <v>0.079</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.656</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="C10">
-        <v>0.734</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="D10">
         <v>0.188</v>
       </c>
       <c r="E10">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C11">
-        <v>0.617</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="D11">
         <v>0.317</v>
       </c>
       <c r="E11">
-        <v>0.067</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -621,24 +634,24 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="C13">
-        <v>0.492</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="D13">
-        <v>0.356</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="E13">
         <v>0.153</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -646,16 +659,16 @@
         <v>0.433</v>
       </c>
       <c r="C14">
-        <v>0.583</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="D14">
-        <v>0.267</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="E14">
         <v>0.15</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -663,50 +676,50 @@
         <v>0.435</v>
       </c>
       <c r="C15">
-        <v>0.5479999999999999</v>
+        <v>0.54799999999999993</v>
       </c>
       <c r="D15">
-        <v>0.339</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="E15">
         <v>0.113</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.506</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="C16">
-        <v>0.608</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="D16">
-        <v>0.291</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="E16">
-        <v>0.101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.462</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="C17">
-        <v>0.588</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="D17">
-        <v>0.287</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E17">
         <v>0.125</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -714,30 +727,13 @@
         <v>0.442</v>
       </c>
       <c r="C18">
-        <v>0.5580000000000001</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="D18">
-        <v>0.325</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="E18">
-        <v>0.117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
-        <v>0.4415584415584415</v>
-      </c>
-      <c r="C19">
-        <v>0.5584415584415584</v>
-      </c>
-      <c r="D19">
-        <v>0.3246753246753247</v>
-      </c>
-      <c r="E19">
-        <v>0.1168831168831169</v>
+        <v>0.11700000000000001</v>
       </c>
     </row>
   </sheetData>
